--- a/threagile/output/supply-chain/risks.xlsx
+++ b/threagile/output/supply-chain/risks.xlsx
@@ -10,75 +10,75 @@
     <sheet name="VaultNote Threat Model" sheetId="2" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName hidden="true" localSheetId="0" name="_xlnm._FilterDatabase">'VaultNote Threat Model'!$A$1:$T$39</definedName>
+    <definedName hidden="true" localSheetId="0" name="_xlnm._FilterDatabase">'VaultNote Threat Model'!$A$1:$T$80</definedName>
   </definedNames>
   <calcPr calcId="122211"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="397">
+  <si>
+    <t>Impact</t>
+  </si>
   <si>
     <t>Function</t>
   </si>
   <si>
+    <t>Risk Category</t>
+  </si>
+  <si>
+    <t>RAA %</t>
+  </si>
+  <si>
+    <t>Identified Risk</t>
+  </si>
+  <si>
+    <t>Mitigation</t>
+  </si>
+  <si>
+    <t>Justification</t>
+  </si>
+  <si>
+    <t>Likelihood</t>
+  </si>
+  <si>
     <t>CWE</t>
   </si>
   <si>
-    <t>Mitigation</t>
+    <t>Communication Link</t>
+  </si>
+  <si>
+    <t>Action</t>
+  </si>
+  <si>
+    <t>Check</t>
   </si>
   <si>
     <t>ID</t>
   </si>
   <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Ticket</t>
+  </si>
+  <si>
+    <t>Severity</t>
+  </si>
+  <si>
+    <t>Technical Asset</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Checked by</t>
+  </si>
+  <si>
     <t>STRIDE</t>
   </si>
   <si>
-    <t>Likelihood</t>
-  </si>
-  <si>
-    <t>Risk Category</t>
-  </si>
-  <si>
-    <t>Communication Link</t>
-  </si>
-  <si>
-    <t>Identified Risk</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>Checked by</t>
-  </si>
-  <si>
-    <t>Severity</t>
-  </si>
-  <si>
-    <t>Technical Asset</t>
-  </si>
-  <si>
-    <t>RAA %</t>
-  </si>
-  <si>
-    <t>Action</t>
-  </si>
-  <si>
-    <t>Check</t>
-  </si>
-  <si>
-    <t>Justification</t>
-  </si>
-  <si>
-    <t>Ticket</t>
-  </si>
-  <si>
-    <t>Impact</t>
-  </si>
-  <si>
     <t>High</t>
   </si>
   <si>
@@ -103,7 +103,7 @@
     <t/>
   </si>
   <si>
-    <t>39</t>
+    <t>21</t>
   </si>
   <si>
     <t>Exposed Default Credentials: MinIO Object Storage is tagged as intentional-misconfiguration and stores confidential data</t>
@@ -144,7 +144,7 @@
     <t>PostgreSQL Connection</t>
   </si>
   <si>
-    <t>82</t>
+    <t>44</t>
   </si>
   <si>
     <t>SQL/NoSQL-Injection risk at API Server against database PostgreSQL Database via PostgreSQL Connection</t>
@@ -195,7 +195,7 @@
     <t>Nginx Reverse Proxy</t>
   </si>
   <si>
-    <t>2</t>
+    <t>1</t>
   </si>
   <si>
     <t>Lateral Movement via Shared Runtime on Docker Host: assets from 3 trust zones co-located</t>
@@ -237,6 +237,15 @@
     <t>missing-authentication@nginx-proxy&gt;http-to-api-server@nginx-proxy@api-server</t>
   </si>
   <si>
+    <t>Route to ECS API</t>
+  </si>
+  <si>
+    <t>Missing Authentication covering communication link Route to ECS API from AWS API Gateway to API Server</t>
+  </si>
+  <si>
+    <t>missing-authentication@aws-api-gateway&gt;route-to-ecs-api@aws-api-gateway@api-server</t>
+  </si>
+  <si>
     <t>Unlikely</t>
   </si>
   <si>
@@ -252,16 +261,28 @@
     <t>0</t>
   </si>
   <si>
+    <t>Missing Cloud Hardening (AWS) risk at AWS Cloud: CIS Benchmark for AWS</t>
+  </si>
+  <si>
+    <t>Cloud Hardening</t>
+  </si>
+  <si>
+    <t>Apply hardening of all cloud components and services, taking special care to follow the individual risk descriptions (which depend on the cloud provider tags in the model). &lt;br&gt;&lt;br&gt;For &lt;b&gt;Amazon Web Services (AWS)&lt;/b&gt;: Follow the &lt;i&gt;CIS Benchmark for Amazon Web Services&lt;/i&gt; (see also the automated checks of cloud audit tools like &lt;i&gt;"PacBot", "CloudSploit", "CloudMapper", "ScoutSuite", or "Prowler AWS CIS Benchmark Tool"&lt;/i&gt;). &lt;br&gt;For EC2 and other servers running Amazon Linux, follow the &lt;i&gt;CIS Benchmark for Amazon Linux&lt;/i&gt; and switch to IMDSv2. &lt;br&gt;For S3 buckets follow the &lt;i&gt;Security Best Practices for Amazon S3&lt;/i&gt; at &lt;a href="https://docs.aws.amazon.com/AmazonS3/latest/dev/security-best-practices.html"&gt;https://docs.aws.amazon.com/AmazonS3/latest/dev/security-best-practices.html&lt;/a&gt; to avoid accidental leakage. &lt;br&gt;Also take a look at some of these tools: &lt;a href="https://github.com/toniblyx/my-arsenal-of-aws-security-tools"&gt;https://github.com/toniblyx/my-arsenal-of-aws-security-tools&lt;/a&gt; &lt;br&gt;&lt;br&gt;For &lt;b&gt;Microsoft Azure&lt;/b&gt;: Follow the &lt;i&gt;CIS Benchmark for Microsoft Azure&lt;/i&gt; (see also the automated checks of cloud audit tools like &lt;i&gt;"CloudSploit" or "ScoutSuite"&lt;/i&gt;).&lt;br&gt;&lt;br&gt;For &lt;b&gt;Google Cloud Platform&lt;/b&gt;: Follow the &lt;i&gt;CIS Benchmark for Google Cloud Computing Platform&lt;/i&gt; (see also the automated checks of cloud audit tools like &lt;i&gt;"CloudSploit" or "ScoutSuite"&lt;/i&gt;). &lt;br&gt;&lt;br&gt;For &lt;b&gt;Oracle Cloud Platform&lt;/b&gt;: Follow the hardening best practices (see also the automated checks of cloud audit tools like &lt;i&gt;"CloudSploit"&lt;/i&gt;).</t>
+  </si>
+  <si>
+    <t>missing-cloud-hardening@aws-cloud@aws</t>
+  </si>
+  <si>
     <t>Missing Cloud Hardening risk at Docker Host</t>
   </si>
   <si>
-    <t>Cloud Hardening</t>
-  </si>
-  <si>
-    <t>Apply hardening of all cloud components and services, taking special care to follow the individual risk descriptions (which depend on the cloud provider tags in the model). &lt;br&gt;&lt;br&gt;For &lt;b&gt;Amazon Web Services (AWS)&lt;/b&gt;: Follow the &lt;i&gt;CIS Benchmark for Amazon Web Services&lt;/i&gt; (see also the automated checks of cloud audit tools like &lt;i&gt;"PacBot", "CloudSploit", "CloudMapper", "ScoutSuite", or "Prowler AWS CIS Benchmark Tool"&lt;/i&gt;). &lt;br&gt;For EC2 and other servers running Amazon Linux, follow the &lt;i&gt;CIS Benchmark for Amazon Linux&lt;/i&gt; and switch to IMDSv2. &lt;br&gt;For S3 buckets follow the &lt;i&gt;Security Best Practices for Amazon S3&lt;/i&gt; at &lt;a href="https://docs.aws.amazon.com/AmazonS3/latest/dev/security-best-practices.html"&gt;https://docs.aws.amazon.com/AmazonS3/latest/dev/security-best-practices.html&lt;/a&gt; to avoid accidental leakage. &lt;br&gt;Also take a look at some of these tools: &lt;a href="https://github.com/toniblyx/my-arsenal-of-aws-security-tools"&gt;https://github.com/toniblyx/my-arsenal-of-aws-security-tools&lt;/a&gt; &lt;br&gt;&lt;br&gt;For &lt;b&gt;Microsoft Azure&lt;/b&gt;: Follow the &lt;i&gt;CIS Benchmark for Microsoft Azure&lt;/i&gt; (see also the automated checks of cloud audit tools like &lt;i&gt;"CloudSploit" or "ScoutSuite"&lt;/i&gt;).&lt;br&gt;&lt;br&gt;For &lt;b&gt;Google Cloud Platform&lt;/b&gt;: Follow the &lt;i&gt;CIS Benchmark for Google Cloud Computing Platform&lt;/i&gt; (see also the automated checks of cloud audit tools like &lt;i&gt;"CloudSploit" or "ScoutSuite"&lt;/i&gt;). &lt;br&gt;&lt;br&gt;For &lt;b&gt;Oracle Cloud Platform&lt;/b&gt;: Follow the hardening best practices (see also the automated checks of cloud audit tools like &lt;i&gt;"CloudSploit"&lt;/i&gt;).</t>
-  </si>
-  <si>
     <t>missing-cloud-hardening@docker-host</t>
+  </si>
+  <si>
+    <t>Missing Cloud Hardening risk at External CI/CD</t>
+  </si>
+  <si>
+    <t>missing-cloud-hardening@external-cicd</t>
   </si>
   <si>
     <t>CWE-693</t>
@@ -293,7 +314,13 @@
     <t>Missing Hardening</t>
   </si>
   <si>
-    <t>Missing Hardening risk at API Server</t>
+    <t>AWS RDS PostgreSQL</t>
+  </si>
+  <si>
+    <t>54</t>
+  </si>
+  <si>
+    <t>Missing Hardening risk at AWS RDS PostgreSQL</t>
   </si>
   <si>
     <t>System Hardening</t>
@@ -302,73 +329,234 @@
     <t>Try to apply all hardening best practices (like CIS benchmarks, OWASP recommendations, vendor recommendations, DevSec Hardening Framework, DBSAT for Oracle databases, and others).</t>
   </si>
   <si>
-    <t>missing-hardening@api-server</t>
+    <t>missing-hardening@rds-postgresql</t>
+  </si>
+  <si>
+    <t>ECS Container Platform</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>Missing Hardening risk at ECS Container Platform</t>
+  </si>
+  <si>
+    <t>missing-hardening@ecs-platform</t>
   </si>
   <si>
     <t>PostgreSQL Database</t>
   </si>
   <si>
-    <t>100</t>
-  </si>
-  <si>
     <t>Missing Hardening risk at PostgreSQL Database</t>
   </si>
   <si>
     <t>missing-hardening@postgresql-db</t>
   </si>
   <si>
+    <t>CWE-22</t>
+  </si>
+  <si>
+    <t>Path-Traversal</t>
+  </si>
+  <si>
+    <t>MinIO File Storage</t>
+  </si>
+  <si>
+    <t>Path-Traversal risk at API Server against filesystem MinIO Object Storage via MinIO File Storage</t>
+  </si>
+  <si>
+    <t>Path-Traversal Prevention</t>
+  </si>
+  <si>
+    <t>Before accessing the file cross-check that it resides in the expected folder and is of the expected type and filename/suffix. Try to use a mapping if possible instead of directly accessing by a filename which is (partly or fully) provided by the caller. When a third-party product is used instead of custom developed software, check if the product applies the proper mitigation and ensure a reasonable patch-level.</t>
+  </si>
+  <si>
+    <t>path-traversal@api-server@minio-storage@api-server&gt;minio-file-storage</t>
+  </si>
+  <si>
+    <t>Pull Images from ECR</t>
+  </si>
+  <si>
+    <t>Path-Traversal risk at ECS Container Platform against filesystem AWS ECR Container Registry via Pull Images from ECR</t>
+  </si>
+  <si>
+    <t>path-traversal@ecs-platform@container-registry@ecs-platform&gt;pull-images-from-ecr</t>
+  </si>
+  <si>
+    <t>GitHub Actions Build Pipeline</t>
+  </si>
+  <si>
+    <t>Push Image to Registry</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>Path-Traversal risk at GitHub Actions Build Pipeline against filesystem AWS ECR Container Registry via Push Image to Registry</t>
+  </si>
+  <si>
+    <t>path-traversal@build-pipeline@container-registry@build-pipeline&gt;push-image-to-registry</t>
+  </si>
+  <si>
+    <t>CWE-918</t>
+  </si>
+  <si>
+    <t>Server-Side Request Forgery (SSRF)</t>
+  </si>
+  <si>
+    <t>Server-Side Request Forgery (SSRF) risk at API Server server-side web-requesting the target MinIO Object Storage via MinIO File Storage</t>
+  </si>
+  <si>
+    <t>SSRF Prevention</t>
+  </si>
+  <si>
+    <t>Try to avoid constructing the outgoing target URL with caller controllable values. Alternatively use a mapping (whitelist) when accessing outgoing URLs instead of creating them including caller controllable values. When a third-party product is used instead of custom developed software, check if the product applies the proper mitigation and ensure a reasonable patch-level.</t>
+  </si>
+  <si>
+    <t>server-side-request-forgery@api-server@minio-storage@api-server&gt;minio-file-storage</t>
+  </si>
+  <si>
+    <t>Lambda Email Notifier</t>
+  </si>
+  <si>
+    <t>SES Email Send</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Server-Side Request Forgery (SSRF) risk at Lambda Email Notifier server-side web-requesting the target AWS SES via SES Email Send</t>
+  </si>
+  <si>
+    <t>server-side-request-forgery@lambda-notifier@aws-ses@lambda-notifier&gt;ses-email-send</t>
+  </si>
+  <si>
+    <t>Server-Side Request Forgery (SSRF) risk at ECS Container Platform server-side web-requesting the target AWS ECR Container Registry via Pull Images from ECR</t>
+  </si>
+  <si>
+    <t>server-side-request-forgery@ecs-platform@container-registry@ecs-platform&gt;pull-images-from-ecr</t>
+  </si>
+  <si>
+    <t>Server-Side Request Forgery (SSRF) risk at GitHub Actions Build Pipeline server-side web-requesting the target AWS ECR Container Registry via Push Image to Registry</t>
+  </si>
+  <si>
+    <t>server-side-request-forgery@build-pipeline@container-registry@build-pipeline&gt;push-image-to-registry</t>
+  </si>
+  <si>
+    <t>VaultNote Source Repository</t>
+  </si>
+  <si>
+    <t>Push to Pipeline</t>
+  </si>
+  <si>
+    <t>Server-Side Request Forgery (SSRF) risk at VaultNote Source Repository server-side web-requesting the target GitHub Actions Build Pipeline via Push to Pipeline</t>
+  </si>
+  <si>
+    <t>server-side-request-forgery@source-repo@build-pipeline@source-repo&gt;push-to-pipeline</t>
+  </si>
+  <si>
     <t>Low</t>
   </si>
   <si>
-    <t>Redis Cache</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>Missing Hardening risk at Redis Cache</t>
-  </si>
-  <si>
-    <t>missing-hardening@redis-cache</t>
-  </si>
-  <si>
-    <t>CWE-22</t>
-  </si>
-  <si>
-    <t>Path-Traversal</t>
-  </si>
-  <si>
-    <t>MinIO File Storage</t>
-  </si>
-  <si>
-    <t>Path-Traversal risk at API Server against filesystem MinIO Object Storage via MinIO File Storage</t>
-  </si>
-  <si>
-    <t>Path-Traversal Prevention</t>
-  </si>
-  <si>
-    <t>Before accessing the file cross-check that it resides in the expected folder and is of the expected type and filename/suffix. Try to use a mapping if possible instead of directly accessing by a filename which is (partly or fully) provided by the caller. When a third-party product is used instead of custom developed software, check if the product applies the proper mitigation and ensure a reasonable patch-level.</t>
-  </si>
-  <si>
-    <t>path-traversal@api-server@minio-storage@api-server&gt;minio-file-storage</t>
-  </si>
-  <si>
-    <t>CWE-918</t>
-  </si>
-  <si>
-    <t>Server-Side Request Forgery (SSRF)</t>
-  </si>
-  <si>
-    <t>Server-Side Request Forgery (SSRF) risk at API Server server-side web-requesting the target MinIO Object Storage via MinIO File Storage</t>
-  </si>
-  <si>
-    <t>SSRF Prevention</t>
-  </si>
-  <si>
-    <t>Try to avoid constructing the outgoing target URL with caller controllable values. Alternatively use a mapping (whitelist) when accessing outgoing URLs instead of creating them including caller controllable values. When a third-party product is used instead of custom developed software, check if the product applies the proper mitigation and ensure a reasonable patch-level.</t>
-  </si>
-  <si>
-    <t>server-side-request-forgery@api-server@minio-storage@api-server&gt;minio-file-storage</t>
+    <t>LLM Note Summarizer</t>
+  </si>
+  <si>
+    <t>Call RAG Pipeline</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>Server-Side Request Forgery (SSRF) risk at LLM Note Summarizer server-side web-requesting the target Note RAG Pipeline via Call RAG Pipeline</t>
+  </si>
+  <si>
+    <t>server-side-request-forgery@llm-summarizer@rag-pipeline@llm-summarizer&gt;call-rag-pipeline</t>
+  </si>
+  <si>
+    <t>Query Vector Store</t>
+  </si>
+  <si>
+    <t>Server-Side Request Forgery (SSRF) risk at LLM Note Summarizer server-side web-requesting the target VaultNote Vector Store via Query Vector Store</t>
+  </si>
+  <si>
+    <t>server-side-request-forgery@llm-summarizer@vector-store@llm-summarizer&gt;query-vector-store</t>
+  </si>
+  <si>
+    <t>Note RAG Pipeline</t>
+  </si>
+  <si>
+    <t>Retrieve from Vector Store</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>Server-Side Request Forgery (SSRF) risk at Note RAG Pipeline server-side web-requesting the target VaultNote Vector Store via Retrieve from Vector Store</t>
+  </si>
+  <si>
+    <t>server-side-request-forgery@rag-pipeline@vector-store@rag-pipeline&gt;retrieve-from-vector-store</t>
+  </si>
+  <si>
+    <t>CWE-1395</t>
+  </si>
+  <si>
+    <t>Supply Chain - Build Pipeline Without Dependency Vulnerability Scanning</t>
+  </si>
+  <si>
+    <t>No Dependency Scanning: build pipeline GitHub Actions Build Pipeline lacks automated dependency vulnerability scanning</t>
+  </si>
+  <si>
+    <t>Add SCA scanning to CI/CD and block builds with critical/high CVEs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Integrate OWASP Dependency-Check, Grype, Snyk, or language-native equivalents (pip-audit, npm audit, gradle dependencyCheckAnalyze) into every CI pipeline. Set the pipeline to fail on CVSS &gt;= 7.0 (high) findings. Configure Dependabot or Renovate for automated dependency update PRs. Tag the asset has-dependency-scanning once scanning is enforced.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Is dependency vulnerability scanning integrated into the CI/CD pipeline? Are builds blocked when high-severity CVEs are detected in dependencies?
+</t>
+  </si>
+  <si>
+    <t>supply-chain-no-dependency-scanning@build-pipeline</t>
+  </si>
+  <si>
+    <t>CWE-1104</t>
+  </si>
+  <si>
+    <t>Supply Chain - Build Pipeline Without Software Bill of Materials</t>
+  </si>
+  <si>
+    <t>No SBOM: build pipeline GitHub Actions Build Pipeline does not generate a Software Bill of Materials</t>
+  </si>
+  <si>
+    <t>Generate a CycloneDX or SPDX SBOM as part of every build</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Integrate SBOM generation into the CI/CD pipeline using Syft, Trivy, or a language-native tool (e.g. gradle-cyclonedx, cyclonedx-maven-plugin, pip-sbom). Publish SBOMs to an artifact store alongside build artifacts. Submit to a dependency-track or GUAC instance for continuous CVE correlation. Tag the asset has-sbom once generation is verified.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Is a CycloneDX or SPDX SBOM generated for every build artifact? Are SBOMs stored alongside the artifacts they describe?
+</t>
+  </si>
+  <si>
+    <t>supply-chain-no-sbom@build-pipeline</t>
+  </si>
+  <si>
+    <t>In Progress</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Syft SBOM generation step is planned for the GitHub Actions workflow. Will generate CycloneDX format and publish to S3 artifact store alongside images. Blocked on VAULT-130 (branch protection) for pipeline trust reasons.
+</t>
+  </si>
+  <si>
+    <t>2026-04-28</t>
+  </si>
+  <si>
+    <t>Security Team</t>
+  </si>
+  <si>
+    <t>VAULT-131</t>
   </si>
   <si>
     <t>CWE-1076</t>
@@ -397,7 +585,7 @@
     <t>Browser SPA</t>
   </si>
   <si>
-    <t>54</t>
+    <t>29</t>
   </si>
   <si>
     <t>No SAST: custom-developed application Browser SPA lacks static analysis security testing in CI/CD</t>
@@ -406,6 +594,74 @@
     <t>supply-chain-no-sast@browser-spa</t>
   </si>
   <si>
+    <t>No SAST: custom-developed application LLM Note Summarizer lacks static analysis security testing in CI/CD</t>
+  </si>
+  <si>
+    <t>supply-chain-no-sast@llm-summarizer</t>
+  </si>
+  <si>
+    <t>No SAST: custom-developed application Lambda Email Notifier lacks static analysis security testing in CI/CD</t>
+  </si>
+  <si>
+    <t>supply-chain-no-sast@lambda-notifier</t>
+  </si>
+  <si>
+    <t>No SAST: custom-developed application Note RAG Pipeline lacks static analysis security testing in CI/CD</t>
+  </si>
+  <si>
+    <t>supply-chain-no-sast@rag-pipeline</t>
+  </si>
+  <si>
+    <t>CWE-284</t>
+  </si>
+  <si>
+    <t>Supply Chain - Source Code Merged Without Mandatory Peer Review</t>
+  </si>
+  <si>
+    <t>No Code Review Policy: repository VaultNote Source Repository does not require mandatory peer review before merge</t>
+  </si>
+  <si>
+    <t>Require at least one peer code review approval before merging to the default branch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Configure the repository to require at least one approving review from a code owner before a pull request can be merged. Enable CODEOWNERS file enforcement. Set the review count based on code criticality (1 for standard changes, 2 for security-sensitive paths). Ensure reviewers cannot self-approve. Tag the asset has-required-review once the policy is enforced.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Is at least one peer review approval required before merging to the default branch? Can the author approve their own pull request?
+</t>
+  </si>
+  <si>
+    <t>supply-chain-no-code-review@source-repo</t>
+  </si>
+  <si>
+    <t>Supply Chain - Source Code Repository Without Branch Protection</t>
+  </si>
+  <si>
+    <t>No Branch Protection: source repository VaultNote Source Repository lacks branch protection on the default branch</t>
+  </si>
+  <si>
+    <t>Enable branch protection rules on the default branch of all source repositories</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enable branch protection on the default (main/master) branch: require pull request reviews (minimum 1 reviewer), require CI/CD status checks to pass, require signed commits (GPG or SSH), prevent force pushes, and prevent deletion. On GitHub, enable "Require approvals" and "Require status checks to pass before merging". Tag the asset has-branch-protection once rules are verified.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Is the default branch protected from direct pushes? Are pull request approvals and CI status checks required before merging?
+</t>
+  </si>
+  <si>
+    <t>supply-chain-no-branch-protection@source-repo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Branch protection rules (require PR review, require CI status checks, prevent force push) are being configured on the GitHub repository. Target: sprint 22. Currently main branch allows direct push from any contributor with write access.
+</t>
+  </si>
+  <si>
+    <t>VAULT-130</t>
+  </si>
+  <si>
     <t>CWE-319</t>
   </si>
   <si>
@@ -440,9 +696,6 @@
   </si>
   <si>
     <t>unencrypted-communication@nginx-proxy&gt;http-to-api-server@nginx-proxy@api-server</t>
-  </si>
-  <si>
-    <t>In Progress</t>
   </si>
   <si>
     <t xml:space="preserve">Migrating Nginx-to-API communication to mTLS. A separate CA will be provisioned inside the Docker network. PR #47 is in review; target completion sprint 22.
@@ -452,15 +705,63 @@
     <t>2026-04-18</t>
   </si>
   <si>
-    <t>Security Team</t>
-  </si>
-  <si>
     <t>VAULT-102</t>
   </si>
   <si>
     <t>CWE-501</t>
   </si>
   <si>
+    <t>Unguarded Access From Internet</t>
+  </si>
+  <si>
+    <t>Unguarded Access from Internet of API Server by AWS API Gateway via Route to ECS API</t>
+  </si>
+  <si>
+    <t>Encapsulation of Technical Asset</t>
+  </si>
+  <si>
+    <t>Encapsulate the asset behind a guarding service, application, or reverse-proxy. For admin maintenance a bastion-host should be used as a jump-server. For file transfer a store-and-forward-host should be used as an indirect file exchange platform.</t>
+  </si>
+  <si>
+    <t>unguarded-access-from-internet@api-server@aws-api-gateway@aws-api-gateway&gt;route-to-ecs-api</t>
+  </si>
+  <si>
+    <t>AWS ECR Container Registry</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>Unguarded Access from Internet of AWS ECR Container Registry by GitHub Actions Build Pipeline via Push Image to Registry</t>
+  </si>
+  <si>
+    <t>unguarded-access-from-internet@container-registry@build-pipeline@build-pipeline&gt;push-image-to-registry</t>
+  </si>
+  <si>
+    <t>Unguarded Access from Internet of GitHub Actions Build Pipeline by VaultNote Source Repository via Push to Pipeline</t>
+  </si>
+  <si>
+    <t>unguarded-access-from-internet@build-pipeline@source-repo@source-repo&gt;push-to-pipeline</t>
+  </si>
+  <si>
+    <t>Unguarded Access from Internet of Note RAG Pipeline by LLM Note Summarizer via Call RAG Pipeline</t>
+  </si>
+  <si>
+    <t>unguarded-access-from-internet@rag-pipeline@llm-summarizer@llm-summarizer&gt;call-rag-pipeline</t>
+  </si>
+  <si>
+    <t>VaultNote Vector Store</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>Unguarded Access from Internet of VaultNote Vector Store by LLM Note Summarizer via Query Vector Store</t>
+  </si>
+  <si>
+    <t>unguarded-access-from-internet@vector-store@llm-summarizer@llm-summarizer&gt;query-vector-store</t>
+  </si>
+  <si>
     <t>Unguarded Direct Datastore Access</t>
   </si>
   <si>
@@ -476,21 +777,69 @@
     <t>unguarded-direct-datastore-access@api-server&gt;postgresql-connection@api-server@postgresql-db</t>
   </si>
   <si>
+    <t>Unguarded Direct Datastore Access of MinIO Object Storage by API Server via MinIO File Storage</t>
+  </si>
+  <si>
+    <t>unguarded-direct-datastore-access@api-server&gt;minio-file-storage@api-server@minio-storage</t>
+  </si>
+  <si>
+    <t>Redis Cache</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
     <t>Unguarded Direct Datastore Access of Redis Cache by API Server via Redis Session Store</t>
   </si>
   <si>
     <t>unguarded-direct-datastore-access@api-server&gt;redis-session-store@api-server@redis-cache</t>
   </si>
   <si>
-    <t>Unguarded Direct Datastore Access of MinIO Object Storage by API Server via MinIO File Storage</t>
-  </si>
-  <si>
-    <t>unguarded-direct-datastore-access@api-server&gt;minio-file-storage@api-server@minio-storage</t>
+    <t>CWE-200</t>
+  </si>
+  <si>
+    <t>Accidental Secret Leak</t>
+  </si>
+  <si>
+    <t>Accidental Secret Leak(Git) risk at VaultNote Source Repository: Git Leak Prevention</t>
+  </si>
+  <si>
+    <t>Build Pipeline Hardening</t>
+  </si>
+  <si>
+    <t>Establish measures preventing accidental check-in or package-in of secrets into sourcecode repositories and artifact registries. This starts by using good .gitignore and .dockerignore files, but does not stop there. See for example tools like &lt;i&gt;\"git-secrets\"&lt;/i&gt; or &lt;i&gt;\"Talisman\"&lt;/i&gt; to have check-in preventive measures for secrets. Consider also to regularly scan your repositories for secrets accidentally checked-in using scanning tools like &lt;i&gt;"gitleaks"&lt;/i&gt; or &lt;i&gt;"gitrob"&lt;/i&gt;.</t>
+  </si>
+  <si>
+    <t>accidental-secret-leak@source-repo</t>
   </si>
   <si>
     <t>CWE-912</t>
   </si>
   <si>
+    <t>Code Backdooring</t>
+  </si>
+  <si>
+    <t>Code Backdooring risk at AWS ECR Container Registry</t>
+  </si>
+  <si>
+    <t>Reduce the attack surface of backdooring the build pipeline by not directly exposing the build pipeline components on the public internet and also not exposing it in front of unmanaged (out-of-scope) developer clients.Also consider the use of code signing to prevent code modifications.</t>
+  </si>
+  <si>
+    <t>code-backdooring@container-registry</t>
+  </si>
+  <si>
+    <t>Code Backdooring risk at GitHub Actions Build Pipeline</t>
+  </si>
+  <si>
+    <t>code-backdooring@build-pipeline</t>
+  </si>
+  <si>
+    <t>Code Backdooring risk at VaultNote Source Repository</t>
+  </si>
+  <si>
+    <t>code-backdooring@source-repo</t>
+  </si>
+  <si>
     <t>Container Base Image Backdooring</t>
   </si>
   <si>
@@ -527,12 +876,39 @@
     <t>container-baseimage-backdooring@minio-storage</t>
   </si>
   <si>
+    <t>Container Base Image Backdooring risk at Note RAG Pipeline</t>
+  </si>
+  <si>
+    <t>container-baseimage-backdooring@rag-pipeline</t>
+  </si>
+  <si>
     <t>Container Base Image Backdooring risk at Redis Cache</t>
   </si>
   <si>
     <t>container-baseimage-backdooring@redis-cache</t>
   </si>
   <si>
+    <t>Container Base Image Backdooring risk at VaultNote Vector Store</t>
+  </si>
+  <si>
+    <t>container-baseimage-backdooring@vector-store</t>
+  </si>
+  <si>
+    <t>Container Platform Escape</t>
+  </si>
+  <si>
+    <t>Container Platform Escape risk at ECS Container Platform</t>
+  </si>
+  <si>
+    <t>Apply hardening of all container infrastructures. &lt;p&gt;See for example the &lt;i&gt;CIS-Benchmarks for Docker and Kubernetes&lt;/i&gt; as well as the &lt;i&gt;Docker Bench for Security&lt;/i&gt; ( &lt;a href="https://github.com/docker/docker-bench-security"&gt;https://github.com/docker/docker-bench-security&lt;/a&gt; ) or &lt;i&gt;InSpec Checks for Docker and Kubernetes&lt;/i&gt; ( &lt;a href="https://github.com/dev-sec/cis-kubernetes-benchmark"&gt;https://github.com/dev-sec/cis-docker-benchmark&lt;/a&gt; and &lt;a href="https://github.com/dev-sec/cis-kubernetes-benchmark"&gt;https://github.com/dev-sec/cis-kubernetes-benchmark&lt;/a&gt; ). Use only trusted base images, verify digital signatures and apply image creation best practices. Also consider using Google's &lt;b&gt;Distroless&lt;/i&gt; base images or otherwise very small base images. Apply namespace isolation and nod affinity to separate pods from each other in terms of access and nodes the same style as you separate data.</t>
+  </si>
+  <si>
+    <t>Are recommendations from the linked cheat sheet and referenced ASVS or CSVS chapter applied?</t>
+  </si>
+  <si>
+    <t>container-platform-escape@ecs-platform</t>
+  </si>
+  <si>
     <t>CWE-1127</t>
   </si>
   <si>
@@ -540,9 +916,6 @@
   </si>
   <si>
     <t>Missing Build Infrastructure in the threat model (referencing asset API Server as an example)</t>
-  </si>
-  <si>
-    <t>Build Pipeline Hardening</t>
   </si>
   <si>
     <t>Include the build infrastructure in the model.</t>
@@ -663,19 +1036,114 @@
     <t>VAULT-95</t>
   </si>
   <si>
+    <t>CWE-345</t>
+  </si>
+  <si>
+    <t>Supply Chain - Container Images Without Cryptographic Signing</t>
+  </si>
+  <si>
+    <t>Unsigned Container Images: asset ECS Container Platform does not enforce container image signing</t>
+  </si>
+  <si>
+    <t>Sign all container images with Cosign/Sigstore and enforce signature verification at deployment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Use Cosign (sigstore.dev) to sign container images as part of the CI/CD pipeline. Store signatures in a Sigstore transparency log (Rekor). Enforce signature verification using an admission controller (Kyverno, OPA Gatekeeper, Ratify) before containers are allowed to run in Kubernetes. For private ECR/GCR/ACR, enable image signing features native to the registry. Tag the asset has-signed-images once signing and verification are enforced.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Are all container images signed before pushing to the registry? Is signature verification enforced at deployment (admission controller)?
+</t>
+  </si>
+  <si>
+    <t>supply-chain-unsigned-container-image@ecs-platform</t>
+  </si>
+  <si>
+    <t>Unsigned Container Images: asset AWS ECR Container Registry does not enforce container image signing</t>
+  </si>
+  <si>
+    <t>supply-chain-unsigned-container-image@container-registry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cosign/Sigstore image signing is planned post-SBOM (VAULT-131). Signature verification via Kyverno admission controller will be added when EKS migration completes. Current mitigation: ECR repository policy restricts push access to the CI service account only.
+</t>
+  </si>
+  <si>
+    <t>VAULT-132</t>
+  </si>
+  <si>
+    <t>Supply Chain - Container Platform Running Unpinned Base Images</t>
+  </si>
+  <si>
+    <t>Unpinned Base Images: container platform ECS Container Platform may run images without digest pinning</t>
+  </si>
+  <si>
+    <t>Pin all container image references to specific digest hashes (sha256:) in Dockerfiles and Kubernetes manifests</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Replace all image references that use mutable tags with pinned digest references (e.g. FROM ubuntu@sha256:...). Use Renovate or Dependabot to automatically open PRs when new digests are published for pinned images. In Kubernetes, set imagePullPolicy to IfNotPresent and pin images in manifests. Tag the asset has-pinned-base-images once all images are pinned.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Are all container image references pinned to immutable digest hashes? Is an automated tool (Renovate/Dependabot) managing digest updates?
+</t>
+  </si>
+  <si>
+    <t>supply-chain-unpinned-base-images@ecs-platform</t>
+  </si>
+  <si>
+    <t>Unchecked Deployment</t>
+  </si>
+  <si>
+    <t>Unchecked Deployment risk at GitHub Actions Build Pipeline</t>
+  </si>
+  <si>
+    <t>Apply DevSecOps best-practices and use scanning tools to identify vulnerabilities in source- or byte-code,dependencies, container layers, and optionally also via dynamic scans against running test systems.</t>
+  </si>
+  <si>
+    <t>unchecked-deployment@build-pipeline</t>
+  </si>
+  <si>
+    <t>Unchecked Deployment risk at VaultNote Source Repository</t>
+  </si>
+  <si>
+    <t>unchecked-deployment@source-repo</t>
+  </si>
+  <si>
+    <t>Unchecked Deployment risk at AWS ECR Container Registry</t>
+  </si>
+  <si>
+    <t>unchecked-deployment@container-registry</t>
+  </si>
+  <si>
     <t>CWE-311</t>
   </si>
   <si>
     <t>Unencrypted Technical Assets</t>
   </si>
   <si>
+    <t>Unencrypted Technical Asset named AWS RDS PostgreSQL missing end user individual encryption with data-with-end-user-individual-key</t>
+  </si>
+  <si>
+    <t>Encryption of Technical Asset</t>
+  </si>
+  <si>
+    <t>Apply encryption to the technical asset.</t>
+  </si>
+  <si>
+    <t>unencrypted-asset@rds-postgresql</t>
+  </si>
+  <si>
+    <t>AWS S3 Notes Bucket</t>
+  </si>
+  <si>
+    <t>Unencrypted Technical Asset named AWS S3 Notes Bucket</t>
+  </si>
+  <si>
+    <t>unencrypted-asset@s3-notes-bucket</t>
+  </si>
+  <si>
     <t>Unencrypted Technical Asset named Redis Cache</t>
-  </si>
-  <si>
-    <t>Encryption of Technical Asset</t>
-  </si>
-  <si>
-    <t>Apply encryption to the technical asset.</t>
   </si>
   <si>
     <t>unencrypted-asset@redis-cache</t>
@@ -744,6 +1212,27 @@
   </si>
   <si>
     <t>dos-risky-access-across-trust-boundary@postgresql-db@api-server@api-server&gt;postgresql-connection-&gt;</t>
+  </si>
+  <si>
+    <t>Unnecessary Technical Asset</t>
+  </si>
+  <si>
+    <t>Unnecessary Technical Asset named AWS RDS PostgreSQL</t>
+  </si>
+  <si>
+    <t>Attack Surface Reduction</t>
+  </si>
+  <si>
+    <t>Try to avoid using technical assets that do not process or store anything.</t>
+  </si>
+  <si>
+    <t>unnecessary-technical-asset@rds-postgresql</t>
+  </si>
+  <si>
+    <t>Unnecessary Technical Asset named AWS S3 Notes Bucket</t>
+  </si>
+  <si>
+    <t>unnecessary-technical-asset@s3-notes-bucket</t>
   </si>
 </sst>
 </file>
@@ -1276,11 +1765,11 @@
     <col customWidth="true" max="5" min="5" width="17.857142857142854"/>
     <col customWidth="true" max="6" min="6" width="13.571428571428571"/>
     <col customWidth="true" max="7" min="7" width="70.14285714285714"/>
-    <col customWidth="true" max="8" min="8" width="23.857142857142858"/>
-    <col customWidth="true" max="9" min="9" width="25"/>
+    <col customWidth="true" max="8" min="8" width="31.57142857142857"/>
+    <col customWidth="true" max="9" min="9" width="29"/>
     <col customWidth="true" max="10" min="10" width="12"/>
     <col customWidth="true" max="11" min="11" width="75"/>
-    <col customWidth="true" max="12" min="12" width="66.42857142857143"/>
+    <col customWidth="true" max="12" min="12" width="85"/>
     <col customWidth="true" max="13" min="13" width="75"/>
     <col customWidth="true" max="14" min="14" width="40"/>
     <col customWidth="true" max="15" min="15" width="92.14285714285714"/>
@@ -1293,64 +1782,64 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="I1" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="K1" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="N1" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="O1" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="24" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1" s="24" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="F1" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" s="24" t="s">
+      <c r="P1" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q1" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="24" t="s">
+      <c r="R1" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="I1" s="24" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="24" t="s">
+      <c r="S1" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="24" t="s">
         <v>14</v>
-      </c>
-      <c r="K1" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="L1" s="24" t="s">
-        <v>15</v>
-      </c>
-      <c r="M1" s="24" t="s">
-        <v>2</v>
-      </c>
-      <c r="N1" s="24" t="s">
-        <v>16</v>
-      </c>
-      <c r="O1" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="P1" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q1" s="24" t="s">
-        <v>17</v>
-      </c>
-      <c r="R1" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="S1" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="T1" s="24" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="2">
@@ -1668,46 +2157,46 @@
         <v>47</v>
       </c>
       <c r="B7" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I7" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="J7" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="K7" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="D7" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="J7" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="K7" s="19" t="s">
-        <v>77</v>
-      </c>
       <c r="L7" s="23" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="M7" s="23" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="N7" s="23" t="s">
         <v>45</v>
       </c>
       <c r="O7" s="20" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="P7" s="10" t="s">
         <v>34</v>
@@ -1730,46 +2219,46 @@
         <v>47</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>23</v>
       </c>
       <c r="F8" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J8" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="K8" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="L8" s="23" t="s">
         <v>81</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="M8" s="23" t="s">
         <v>82</v>
       </c>
-      <c r="H8" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="I8" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="J8" s="18" t="s">
-        <v>58</v>
-      </c>
-      <c r="K8" s="19" t="s">
+      <c r="N8" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O8" s="20" t="s">
         <v>83</v>
-      </c>
-      <c r="L8" s="23" t="s">
-        <v>84</v>
-      </c>
-      <c r="M8" s="23" t="s">
-        <v>85</v>
-      </c>
-      <c r="N8" s="23" t="s">
-        <v>86</v>
-      </c>
-      <c r="O8" s="20" t="s">
-        <v>87</v>
       </c>
       <c r="P8" s="10" t="s">
         <v>34</v>
@@ -1792,10 +2281,10 @@
         <v>47</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>35</v>
@@ -1804,34 +2293,34 @@
         <v>23</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="I9" s="5" t="s">
         <v>27</v>
       </c>
       <c r="J9" s="18" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="K9" s="19" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="L9" s="23" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="M9" s="23" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="N9" s="23" t="s">
         <v>45</v>
       </c>
       <c r="O9" s="20" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="P9" s="10" t="s">
         <v>34</v>
@@ -1850,50 +2339,50 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="D10" s="6" t="s">
+      <c r="A10" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="F10" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="I10" s="5" t="s">
+      <c r="F10" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="I10" s="7" t="s">
         <v>27</v>
       </c>
       <c r="J10" s="18" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="K10" s="19" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="L10" s="23" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="M10" s="23" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="N10" s="23" t="s">
         <v>45</v>
       </c>
       <c r="O10" s="20" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="P10" s="10" t="s">
         <v>34</v>
@@ -1912,38 +2401,38 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="B11" s="8" t="s">
+      <c r="A11" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="C11" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E11" s="8" t="s">
+      <c r="C11" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F11" s="8" t="s">
+      <c r="F11" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="G11" s="7" t="s">
+      <c r="G11" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="H11" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="I11" s="7" t="s">
+      <c r="H11" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="I11" s="5" t="s">
         <v>27</v>
       </c>
       <c r="J11" s="18" t="s">
-        <v>100</v>
+        <v>58</v>
       </c>
       <c r="K11" s="19" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="L11" s="23" t="s">
         <v>91</v>
@@ -1952,10 +2441,10 @@
         <v>92</v>
       </c>
       <c r="N11" s="23" t="s">
-        <v>45</v>
+        <v>93</v>
       </c>
       <c r="O11" s="20" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="P11" s="10" t="s">
         <v>34</v>
@@ -1978,46 +2467,46 @@
         <v>47</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>48</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>39</v>
+        <v>97</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>105</v>
+        <v>27</v>
       </c>
       <c r="J12" s="18" t="s">
-        <v>41</v>
+        <v>98</v>
       </c>
       <c r="K12" s="19" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="L12" s="23" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="M12" s="23" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="N12" s="23" t="s">
         <v>45</v>
       </c>
       <c r="O12" s="20" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="P12" s="10" t="s">
         <v>34</v>
@@ -2046,40 +2535,40 @@
         <v>48</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>39</v>
+        <v>103</v>
       </c>
       <c r="I13" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J13" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="K13" s="19" t="s">
         <v>105</v>
       </c>
-      <c r="J13" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="K13" s="19" t="s">
-        <v>112</v>
-      </c>
       <c r="L13" s="23" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="M13" s="23" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="N13" s="23" t="s">
         <v>45</v>
       </c>
       <c r="O13" s="20" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="P13" s="10" t="s">
         <v>34</v>
@@ -2111,37 +2600,37 @@
         <v>35</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>116</v>
+        <v>95</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>117</v>
+        <v>96</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>39</v>
+        <v>107</v>
       </c>
       <c r="I14" s="5" t="s">
         <v>27</v>
       </c>
       <c r="J14" s="18" t="s">
-        <v>41</v>
+        <v>98</v>
       </c>
       <c r="K14" s="19" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="L14" s="23" t="s">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="M14" s="23" t="s">
-        <v>120</v>
+        <v>101</v>
       </c>
       <c r="N14" s="23" t="s">
-        <v>121</v>
+        <v>45</v>
       </c>
       <c r="O14" s="20" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="P14" s="10" t="s">
         <v>34</v>
@@ -2164,46 +2653,46 @@
         <v>47</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>48</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>36</v>
       </c>
       <c r="F15" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="J15" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="K15" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="L15" s="23" t="s">
+        <v>114</v>
+      </c>
+      <c r="M15" s="23" t="s">
+        <v>115</v>
+      </c>
+      <c r="N15" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O15" s="20" t="s">
         <v>116</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="H15" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="I15" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="J15" s="18" t="s">
-        <v>124</v>
-      </c>
-      <c r="K15" s="19" t="s">
-        <v>125</v>
-      </c>
-      <c r="L15" s="23" t="s">
-        <v>119</v>
-      </c>
-      <c r="M15" s="23" t="s">
-        <v>120</v>
-      </c>
-      <c r="N15" s="23" t="s">
-        <v>121</v>
-      </c>
-      <c r="O15" s="20" t="s">
-        <v>126</v>
       </c>
       <c r="P15" s="10" t="s">
         <v>34</v>
@@ -2229,43 +2718,43 @@
         <v>52</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>127</v>
+        <v>110</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>39</v>
+        <v>103</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="J16" s="18" t="s">
-        <v>41</v>
+        <v>104</v>
       </c>
       <c r="K16" s="19" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="L16" s="23" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="M16" s="23" t="s">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="N16" s="23" t="s">
         <v>45</v>
       </c>
       <c r="O16" s="20" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="P16" s="10" t="s">
         <v>34</v>
@@ -2291,43 +2780,43 @@
         <v>52</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>127</v>
+        <v>110</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>39</v>
+        <v>120</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>40</v>
+        <v>121</v>
       </c>
       <c r="J17" s="18" t="s">
-        <v>41</v>
+        <v>122</v>
       </c>
       <c r="K17" s="19" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="L17" s="23" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="M17" s="23" t="s">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="N17" s="23" t="s">
         <v>45</v>
       </c>
       <c r="O17" s="20" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="P17" s="10" t="s">
         <v>34</v>
@@ -2353,43 +2842,43 @@
         <v>52</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H18" s="5" t="s">
         <v>39</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>49</v>
+        <v>112</v>
       </c>
       <c r="J18" s="18" t="s">
         <v>41</v>
       </c>
       <c r="K18" s="19" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="L18" s="23" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="M18" s="23" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="N18" s="23" t="s">
         <v>45</v>
       </c>
       <c r="O18" s="20" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="P18" s="10" t="s">
         <v>34</v>
@@ -2421,99 +2910,99 @@
         <v>22</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G19" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="J19" s="18" t="s">
+        <v>133</v>
+      </c>
+      <c r="K19" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="L19" s="23" t="s">
         <v>128</v>
       </c>
-      <c r="H19" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="I19" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="J19" s="18" t="s">
-        <v>58</v>
-      </c>
-      <c r="K19" s="19" t="s">
-        <v>137</v>
-      </c>
-      <c r="L19" s="23" t="s">
-        <v>130</v>
-      </c>
       <c r="M19" s="23" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="N19" s="23" t="s">
         <v>45</v>
       </c>
       <c r="O19" s="20" t="s">
-        <v>138</v>
-      </c>
-      <c r="P19" s="12" t="s">
-        <v>139</v>
+        <v>135</v>
+      </c>
+      <c r="P19" s="10" t="s">
+        <v>34</v>
       </c>
       <c r="Q19" s="19" t="s">
-        <v>140</v>
+        <v>27</v>
       </c>
       <c r="R19" s="17" t="s">
-        <v>141</v>
+        <v>27</v>
       </c>
       <c r="S19" s="17" t="s">
-        <v>142</v>
+        <v>27</v>
       </c>
       <c r="T19" s="16" t="s">
-        <v>143</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="F20" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="H20" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="I20" s="5" t="s">
-        <v>40</v>
+      <c r="A20" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="H20" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="I20" s="7" t="s">
+        <v>117</v>
       </c>
       <c r="J20" s="18" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="K20" s="19" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="L20" s="23" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="M20" s="23" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="N20" s="23" t="s">
         <v>45</v>
       </c>
       <c r="O20" s="20" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="P20" s="10" t="s">
         <v>34</v>
@@ -2532,50 +3021,50 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="F21" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="H21" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="I21" s="5" t="s">
-        <v>49</v>
+      <c r="A21" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="I21" s="7" t="s">
+        <v>121</v>
       </c>
       <c r="J21" s="18" t="s">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="K21" s="19" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="L21" s="23" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="M21" s="23" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="N21" s="23" t="s">
         <v>45</v>
       </c>
       <c r="O21" s="20" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="P21" s="10" t="s">
         <v>34</v>
@@ -2598,46 +3087,46 @@
         <v>48</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>98</v>
+        <v>48</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>64</v>
+        <v>22</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>144</v>
+        <v>125</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>145</v>
+        <v>126</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>26</v>
+        <v>140</v>
       </c>
       <c r="I22" s="7" t="s">
-        <v>105</v>
+        <v>141</v>
       </c>
       <c r="J22" s="18" t="s">
-        <v>28</v>
+        <v>122</v>
       </c>
       <c r="K22" s="19" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="L22" s="23" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="M22" s="23" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="N22" s="23" t="s">
         <v>45</v>
       </c>
       <c r="O22" s="20" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="P22" s="10" t="s">
         <v>34</v>
@@ -2660,46 +3149,46 @@
         <v>48</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>20</v>
+        <v>144</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>154</v>
+        <v>125</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>155</v>
+        <v>126</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>39</v>
+        <v>145</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>27</v>
+        <v>146</v>
       </c>
       <c r="J23" s="18" t="s">
-        <v>41</v>
+        <v>147</v>
       </c>
       <c r="K23" s="19" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="L23" s="23" t="s">
-        <v>157</v>
+        <v>128</v>
       </c>
       <c r="M23" s="23" t="s">
-        <v>158</v>
+        <v>129</v>
       </c>
       <c r="N23" s="23" t="s">
-        <v>159</v>
+        <v>45</v>
       </c>
       <c r="O23" s="20" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="P23" s="10" t="s">
         <v>34</v>
@@ -2722,46 +3211,46 @@
         <v>48</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>20</v>
+        <v>144</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>154</v>
+        <v>125</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>155</v>
+        <v>126</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>57</v>
+        <v>145</v>
       </c>
       <c r="I24" s="7" t="s">
-        <v>27</v>
+        <v>150</v>
       </c>
       <c r="J24" s="18" t="s">
-        <v>58</v>
+        <v>147</v>
       </c>
       <c r="K24" s="19" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="L24" s="23" t="s">
-        <v>157</v>
+        <v>128</v>
       </c>
       <c r="M24" s="23" t="s">
-        <v>158</v>
+        <v>129</v>
       </c>
       <c r="N24" s="23" t="s">
-        <v>159</v>
+        <v>45</v>
       </c>
       <c r="O24" s="20" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="P24" s="10" t="s">
         <v>34</v>
@@ -2784,790 +3273,790 @@
         <v>48</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="C25" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="H25" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="I25" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="J25" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="K25" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="L25" s="23" t="s">
+        <v>128</v>
+      </c>
+      <c r="M25" s="23" t="s">
+        <v>129</v>
+      </c>
+      <c r="N25" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O25" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="P25" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q25" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R25" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S25" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T25" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C26" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D25" s="8" t="s">
+      <c r="D26" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E25" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="F25" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="G25" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="H25" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="I25" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="J25" s="18" t="s">
-        <v>95</v>
-      </c>
-      <c r="K25" s="19" t="s">
+      <c r="E26" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="I26" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J26" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="K26" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="L26" s="23" t="s">
+        <v>161</v>
+      </c>
+      <c r="M26" s="23" t="s">
+        <v>162</v>
+      </c>
+      <c r="N26" s="23" t="s">
         <v>163</v>
       </c>
-      <c r="L25" s="23" t="s">
-        <v>157</v>
-      </c>
-      <c r="M25" s="23" t="s">
-        <v>158</v>
-      </c>
-      <c r="N25" s="23" t="s">
-        <v>159</v>
-      </c>
-      <c r="O25" s="20" t="s">
+      <c r="O26" s="20" t="s">
         <v>164</v>
       </c>
-      <c r="P25" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q25" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="R25" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="S25" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="T25" s="16" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="B26" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="D26" s="8" t="s">
+      <c r="P26" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q26" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R26" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S26" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T26" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D27" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E26" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="F26" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="G26" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="H26" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="I26" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="J26" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="K26" s="19" t="s">
+      <c r="E27" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F27" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="L26" s="23" t="s">
-        <v>157</v>
-      </c>
-      <c r="M26" s="23" t="s">
-        <v>158</v>
-      </c>
-      <c r="N26" s="23" t="s">
-        <v>159</v>
-      </c>
-      <c r="O26" s="20" t="s">
+      <c r="G27" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="P26" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q26" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="R26" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="S26" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="T26" s="16" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="B27" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C27" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="D27" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E27" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="F27" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="G27" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="H27" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="I27" s="7" t="s">
+      <c r="H27" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="I27" s="5" t="s">
         <v>27</v>
       </c>
       <c r="J27" s="18" t="s">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="K27" s="19" t="s">
         <v>167</v>
       </c>
       <c r="L27" s="23" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="M27" s="23" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="N27" s="23" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="O27" s="20" t="s">
-        <v>168</v>
-      </c>
-      <c r="P27" s="10" t="s">
-        <v>34</v>
+        <v>171</v>
+      </c>
+      <c r="P27" s="12" t="s">
+        <v>172</v>
       </c>
       <c r="Q27" s="19" t="s">
-        <v>27</v>
+        <v>173</v>
       </c>
       <c r="R27" s="17" t="s">
-        <v>27</v>
+        <v>174</v>
       </c>
       <c r="S27" s="17" t="s">
-        <v>27</v>
+        <v>175</v>
       </c>
       <c r="T27" s="16" t="s">
-        <v>27</v>
+        <v>176</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="B28" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C28" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="D28" s="8" t="s">
+      <c r="A28" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D28" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E28" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="F28" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="G28" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="H28" s="7" t="s">
+      <c r="E28" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="H28" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="I28" s="7" t="s">
+      <c r="I28" s="5" t="s">
         <v>27</v>
       </c>
       <c r="J28" s="18" t="s">
         <v>41</v>
       </c>
       <c r="K28" s="19" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="L28" s="23" t="s">
+        <v>180</v>
+      </c>
+      <c r="M28" s="23" t="s">
+        <v>181</v>
+      </c>
+      <c r="N28" s="23" t="s">
+        <v>182</v>
+      </c>
+      <c r="O28" s="20" t="s">
+        <v>183</v>
+      </c>
+      <c r="P28" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q28" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R28" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S28" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T28" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="H29" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="I29" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J29" s="18" t="s">
+        <v>185</v>
+      </c>
+      <c r="K29" s="19" t="s">
+        <v>186</v>
+      </c>
+      <c r="L29" s="23" t="s">
+        <v>180</v>
+      </c>
+      <c r="M29" s="23" t="s">
+        <v>181</v>
+      </c>
+      <c r="N29" s="23" t="s">
+        <v>182</v>
+      </c>
+      <c r="O29" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="P29" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q29" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R29" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S29" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T29" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="H30" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="I30" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J30" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="K30" s="19" t="s">
+        <v>188</v>
+      </c>
+      <c r="L30" s="23" t="s">
+        <v>180</v>
+      </c>
+      <c r="M30" s="23" t="s">
+        <v>181</v>
+      </c>
+      <c r="N30" s="23" t="s">
+        <v>182</v>
+      </c>
+      <c r="O30" s="20" t="s">
+        <v>189</v>
+      </c>
+      <c r="P30" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q30" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R30" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S30" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T30" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="G31" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="H31" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="I31" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J31" s="18" t="s">
+        <v>133</v>
+      </c>
+      <c r="K31" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="L31" s="23" t="s">
+        <v>180</v>
+      </c>
+      <c r="M31" s="23" t="s">
+        <v>181</v>
+      </c>
+      <c r="N31" s="23" t="s">
+        <v>182</v>
+      </c>
+      <c r="O31" s="20" t="s">
+        <v>191</v>
+      </c>
+      <c r="P31" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q31" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R31" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S31" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T31" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="G32" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="H32" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="I32" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J32" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="K32" s="19" t="s">
+        <v>192</v>
+      </c>
+      <c r="L32" s="23" t="s">
+        <v>180</v>
+      </c>
+      <c r="M32" s="23" t="s">
+        <v>181</v>
+      </c>
+      <c r="N32" s="23" t="s">
+        <v>182</v>
+      </c>
+      <c r="O32" s="20" t="s">
+        <v>193</v>
+      </c>
+      <c r="P32" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q32" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R32" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S32" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T32" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="G33" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="H33" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="I33" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J33" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="K33" s="19" t="s">
+        <v>196</v>
+      </c>
+      <c r="L33" s="23" t="s">
+        <v>197</v>
+      </c>
+      <c r="M33" s="23" t="s">
+        <v>198</v>
+      </c>
+      <c r="N33" s="23" t="s">
+        <v>199</v>
+      </c>
+      <c r="O33" s="20" t="s">
+        <v>200</v>
+      </c>
+      <c r="P33" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q33" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R33" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S33" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T33" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="G34" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="H34" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="I34" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J34" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="K34" s="19" t="s">
+        <v>202</v>
+      </c>
+      <c r="L34" s="23" t="s">
+        <v>203</v>
+      </c>
+      <c r="M34" s="23" t="s">
+        <v>204</v>
+      </c>
+      <c r="N34" s="23" t="s">
+        <v>205</v>
+      </c>
+      <c r="O34" s="20" t="s">
+        <v>206</v>
+      </c>
+      <c r="P34" s="12" t="s">
         <v>172</v>
       </c>
-      <c r="M28" s="23" t="s">
-        <v>173</v>
-      </c>
-      <c r="N28" s="23" t="s">
-        <v>45</v>
-      </c>
-      <c r="O28" s="20" t="s">
+      <c r="Q34" s="19" t="s">
+        <v>207</v>
+      </c>
+      <c r="R34" s="17" t="s">
         <v>174</v>
       </c>
-      <c r="P28" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q28" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="R28" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="S28" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="T28" s="16" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="B29" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="D29" s="8" t="s">
+      <c r="S34" s="17" t="s">
         <v>175</v>
       </c>
-      <c r="E29" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="F29" s="8" t="s">
-        <v>176</v>
-      </c>
-      <c r="G29" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="H29" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="I29" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="J29" s="18" t="s">
-        <v>58</v>
-      </c>
-      <c r="K29" s="19" t="s">
-        <v>178</v>
-      </c>
-      <c r="L29" s="23" t="s">
-        <v>179</v>
-      </c>
-      <c r="M29" s="23" t="s">
-        <v>180</v>
-      </c>
-      <c r="N29" s="23" t="s">
-        <v>45</v>
-      </c>
-      <c r="O29" s="20" t="s">
-        <v>181</v>
-      </c>
-      <c r="P29" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q29" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="R29" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="S29" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="T29" s="16" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="B30" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C30" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="D30" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="E30" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="F30" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="G30" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="H30" s="7" t="s">
+      <c r="T34" s="16" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="G35" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="H35" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="I30" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="J30" s="18" t="s">
+      <c r="I35" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="J35" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="K30" s="19" t="s">
-        <v>185</v>
-      </c>
-      <c r="L30" s="23" t="s">
-        <v>186</v>
-      </c>
-      <c r="M30" s="23" t="s">
-        <v>187</v>
-      </c>
-      <c r="N30" s="23" t="s">
-        <v>45</v>
-      </c>
-      <c r="O30" s="20" t="s">
-        <v>188</v>
-      </c>
-      <c r="P30" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q30" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="R30" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="S30" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="T30" s="16" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="B31" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C31" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="D31" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="E31" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="F31" s="8" t="s">
-        <v>189</v>
-      </c>
-      <c r="G31" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="H31" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="I31" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="J31" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="K31" s="19" t="s">
-        <v>191</v>
-      </c>
-      <c r="L31" s="23" t="s">
-        <v>192</v>
-      </c>
-      <c r="M31" s="23" t="s">
-        <v>193</v>
-      </c>
-      <c r="N31" s="23" t="s">
-        <v>194</v>
-      </c>
-      <c r="O31" s="20" t="s">
-        <v>195</v>
-      </c>
-      <c r="P31" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q31" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="R31" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="S31" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="T31" s="16" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="B32" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C32" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="D32" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E32" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="F32" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="G32" s="7" t="s">
-        <v>196</v>
-      </c>
-      <c r="H32" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="I32" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="J32" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="K32" s="19" t="s">
-        <v>197</v>
-      </c>
-      <c r="L32" s="23" t="s">
-        <v>198</v>
-      </c>
-      <c r="M32" s="23" t="s">
-        <v>199</v>
-      </c>
-      <c r="N32" s="23" t="s">
-        <v>200</v>
-      </c>
-      <c r="O32" s="20" t="s">
-        <v>201</v>
-      </c>
-      <c r="P32" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q32" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="R32" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="S32" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="T32" s="16" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="B33" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C33" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="D33" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="E33" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="F33" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="G33" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="H33" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="I33" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="J33" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="K33" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="L33" s="23" t="s">
-        <v>204</v>
-      </c>
-      <c r="M33" s="23" t="s">
-        <v>205</v>
-      </c>
-      <c r="N33" s="23" t="s">
-        <v>45</v>
-      </c>
-      <c r="O33" s="20" t="s">
-        <v>206</v>
-      </c>
-      <c r="P33" s="13" t="s">
-        <v>207</v>
-      </c>
-      <c r="Q33" s="19" t="s">
-        <v>208</v>
-      </c>
-      <c r="R33" s="17" t="s">
-        <v>209</v>
-      </c>
-      <c r="S33" s="17" t="s">
-        <v>210</v>
-      </c>
-      <c r="T33" s="16" t="s">
+      <c r="K35" s="19" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="B34" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C34" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="D34" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="E34" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="F34" s="8" t="s">
+      <c r="L35" s="23" t="s">
         <v>212</v>
       </c>
-      <c r="G34" s="7" t="s">
+      <c r="M35" s="23" t="s">
         <v>213</v>
-      </c>
-      <c r="H34" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="I34" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="J34" s="18" t="s">
-        <v>100</v>
-      </c>
-      <c r="K34" s="19" t="s">
-        <v>214</v>
-      </c>
-      <c r="L34" s="23" t="s">
-        <v>215</v>
-      </c>
-      <c r="M34" s="23" t="s">
-        <v>216</v>
-      </c>
-      <c r="N34" s="23" t="s">
-        <v>45</v>
-      </c>
-      <c r="O34" s="20" t="s">
-        <v>217</v>
-      </c>
-      <c r="P34" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q34" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="R34" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="S34" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="T34" s="16" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="B35" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C35" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D35" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="E35" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="F35" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="G35" s="7" t="s">
-        <v>213</v>
-      </c>
-      <c r="H35" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="I35" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="J35" s="18" t="s">
-        <v>95</v>
-      </c>
-      <c r="K35" s="19" t="s">
-        <v>218</v>
-      </c>
-      <c r="L35" s="23" t="s">
-        <v>215</v>
-      </c>
-      <c r="M35" s="23" t="s">
-        <v>216</v>
       </c>
       <c r="N35" s="23" t="s">
         <v>45</v>
       </c>
       <c r="O35" s="20" t="s">
-        <v>219</v>
-      </c>
-      <c r="P35" s="13" t="s">
-        <v>207</v>
+        <v>214</v>
+      </c>
+      <c r="P35" s="10" t="s">
+        <v>34</v>
       </c>
       <c r="Q35" s="19" t="s">
-        <v>220</v>
+        <v>27</v>
       </c>
       <c r="R35" s="17" t="s">
-        <v>221</v>
+        <v>27</v>
       </c>
       <c r="S35" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T35" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="G36" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="T35" s="16" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="B36" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C36" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="D36" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="E36" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="F36" s="8" t="s">
+      <c r="H36" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I36" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="J36" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="K36" s="19" t="s">
+        <v>215</v>
+      </c>
+      <c r="L36" s="23" t="s">
         <v>212</v>
       </c>
-      <c r="G36" s="7" t="s">
+      <c r="M36" s="23" t="s">
         <v>213</v>
-      </c>
-      <c r="H36" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="I36" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="J36" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="K36" s="19" t="s">
-        <v>223</v>
-      </c>
-      <c r="L36" s="23" t="s">
-        <v>215</v>
-      </c>
-      <c r="M36" s="23" t="s">
-        <v>216</v>
       </c>
       <c r="N36" s="23" t="s">
         <v>45</v>
       </c>
       <c r="O36" s="20" t="s">
-        <v>224</v>
-      </c>
-      <c r="P36" s="12" t="s">
-        <v>139</v>
+        <v>216</v>
+      </c>
+      <c r="P36" s="10" t="s">
+        <v>34</v>
       </c>
       <c r="Q36" s="19" t="s">
-        <v>225</v>
+        <v>27</v>
       </c>
       <c r="R36" s="17" t="s">
-        <v>141</v>
+        <v>27</v>
       </c>
       <c r="S36" s="17" t="s">
-        <v>142</v>
+        <v>27</v>
       </c>
       <c r="T36" s="16" t="s">
-        <v>226</v>
+        <v>27</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="B37" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="C37" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="D37" s="10" t="s">
-        <v>227</v>
-      </c>
-      <c r="E37" s="10" t="s">
+      <c r="A37" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E37" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F37" s="10" t="s">
-        <v>228</v>
-      </c>
-      <c r="G37" s="9" t="s">
-        <v>229</v>
-      </c>
-      <c r="H37" s="9" t="s">
+      <c r="F37" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="G37" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="H37" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="I37" s="9" t="s">
-        <v>230</v>
+      <c r="I37" s="5" t="s">
+        <v>49</v>
       </c>
       <c r="J37" s="18" t="s">
         <v>41</v>
       </c>
       <c r="K37" s="19" t="s">
-        <v>231</v>
+        <v>217</v>
       </c>
       <c r="L37" s="23" t="s">
-        <v>232</v>
+        <v>212</v>
       </c>
       <c r="M37" s="23" t="s">
-        <v>233</v>
+        <v>213</v>
       </c>
       <c r="N37" s="23" t="s">
         <v>45</v>
       </c>
       <c r="O37" s="20" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="P37" s="10" t="s">
         <v>34</v>
@@ -3586,131 +4075,2673 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="B38" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="C38" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="D38" s="10" t="s">
-        <v>227</v>
-      </c>
-      <c r="E38" s="10" t="s">
+      <c r="A38" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E38" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F38" s="10" t="s">
-        <v>228</v>
-      </c>
-      <c r="G38" s="9" t="s">
-        <v>229</v>
-      </c>
-      <c r="H38" s="9" t="s">
+      <c r="F38" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="G38" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="H38" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="I38" s="9" t="s">
-        <v>230</v>
+      <c r="I38" s="5" t="s">
+        <v>67</v>
       </c>
       <c r="J38" s="18" t="s">
         <v>58</v>
       </c>
       <c r="K38" s="19" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
       <c r="L38" s="23" t="s">
-        <v>232</v>
+        <v>212</v>
       </c>
       <c r="M38" s="23" t="s">
-        <v>233</v>
+        <v>213</v>
       </c>
       <c r="N38" s="23" t="s">
         <v>45</v>
       </c>
       <c r="O38" s="20" t="s">
-        <v>236</v>
-      </c>
-      <c r="P38" s="10" t="s">
-        <v>34</v>
+        <v>220</v>
+      </c>
+      <c r="P38" s="12" t="s">
+        <v>172</v>
       </c>
       <c r="Q38" s="19" t="s">
-        <v>27</v>
+        <v>221</v>
       </c>
       <c r="R38" s="17" t="s">
-        <v>27</v>
+        <v>222</v>
       </c>
       <c r="S38" s="17" t="s">
-        <v>27</v>
+        <v>175</v>
       </c>
       <c r="T38" s="16" t="s">
-        <v>27</v>
+        <v>223</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="B39" s="10" t="s">
+      <c r="A39" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F39" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="G39" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="H39" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I39" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="C39" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="D39" s="10" t="s">
+      <c r="J39" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="K39" s="19" t="s">
+        <v>226</v>
+      </c>
+      <c r="L39" s="23" t="s">
         <v>227</v>
       </c>
-      <c r="E39" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="F39" s="10" t="s">
+      <c r="M39" s="23" t="s">
         <v>228</v>
-      </c>
-      <c r="G39" s="9" t="s">
-        <v>229</v>
-      </c>
-      <c r="H39" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="I39" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="J39" s="18" t="s">
-        <v>95</v>
-      </c>
-      <c r="K39" s="19" t="s">
-        <v>237</v>
-      </c>
-      <c r="L39" s="23" t="s">
-        <v>232</v>
-      </c>
-      <c r="M39" s="23" t="s">
-        <v>233</v>
       </c>
       <c r="N39" s="23" t="s">
         <v>45</v>
       </c>
       <c r="O39" s="20" t="s">
+        <v>229</v>
+      </c>
+      <c r="P39" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q39" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R39" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S39" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T39" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F40" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="G40" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="H40" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="I40" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="J40" s="18" t="s">
+        <v>231</v>
+      </c>
+      <c r="K40" s="19" t="s">
+        <v>232</v>
+      </c>
+      <c r="L40" s="23" t="s">
+        <v>227</v>
+      </c>
+      <c r="M40" s="23" t="s">
+        <v>228</v>
+      </c>
+      <c r="N40" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O40" s="20" t="s">
+        <v>233</v>
+      </c>
+      <c r="P40" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q40" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R40" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S40" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T40" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="E41" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F41" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="G41" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="H41" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="I41" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="J41" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="K41" s="19" t="s">
+        <v>234</v>
+      </c>
+      <c r="L41" s="23" t="s">
+        <v>227</v>
+      </c>
+      <c r="M41" s="23" t="s">
+        <v>228</v>
+      </c>
+      <c r="N41" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O41" s="20" t="s">
+        <v>235</v>
+      </c>
+      <c r="P41" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q41" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R41" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S41" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T41" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="E42" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F42" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="G42" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="H42" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="I42" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="J42" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="K42" s="19" t="s">
+        <v>236</v>
+      </c>
+      <c r="L42" s="23" t="s">
+        <v>227</v>
+      </c>
+      <c r="M42" s="23" t="s">
+        <v>228</v>
+      </c>
+      <c r="N42" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O42" s="20" t="s">
+        <v>237</v>
+      </c>
+      <c r="P42" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q42" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R42" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S42" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T42" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C43" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="E43" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F43" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="G43" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="H43" s="7" t="s">
         <v>238</v>
       </c>
-      <c r="P39" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q39" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="R39" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="S39" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="T39" s="16" t="s">
+      <c r="I43" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="J43" s="18" t="s">
+        <v>239</v>
+      </c>
+      <c r="K43" s="19" t="s">
+        <v>240</v>
+      </c>
+      <c r="L43" s="23" t="s">
+        <v>227</v>
+      </c>
+      <c r="M43" s="23" t="s">
+        <v>228</v>
+      </c>
+      <c r="N43" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O43" s="20" t="s">
+        <v>241</v>
+      </c>
+      <c r="P43" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q43" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R43" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S43" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T43" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F44" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="G44" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="H44" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="I44" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="J44" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="K44" s="19" t="s">
+        <v>243</v>
+      </c>
+      <c r="L44" s="23" t="s">
+        <v>244</v>
+      </c>
+      <c r="M44" s="23" t="s">
+        <v>245</v>
+      </c>
+      <c r="N44" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O44" s="20" t="s">
+        <v>246</v>
+      </c>
+      <c r="P44" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q44" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R44" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S44" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T44" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C45" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F45" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="G45" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="H45" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="I45" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="J45" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="K45" s="19" t="s">
+        <v>247</v>
+      </c>
+      <c r="L45" s="23" t="s">
+        <v>244</v>
+      </c>
+      <c r="M45" s="23" t="s">
+        <v>245</v>
+      </c>
+      <c r="N45" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O45" s="20" t="s">
+        <v>248</v>
+      </c>
+      <c r="P45" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q45" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R45" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S45" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T45" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F46" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="G46" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="H46" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="I46" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="J46" s="18" t="s">
+        <v>250</v>
+      </c>
+      <c r="K46" s="19" t="s">
+        <v>251</v>
+      </c>
+      <c r="L46" s="23" t="s">
+        <v>244</v>
+      </c>
+      <c r="M46" s="23" t="s">
+        <v>245</v>
+      </c>
+      <c r="N46" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O46" s="20" t="s">
+        <v>252</v>
+      </c>
+      <c r="P46" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q46" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R46" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S46" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T46" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C47" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D47" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E47" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F47" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="G47" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="H47" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="I47" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J47" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="K47" s="19" t="s">
+        <v>255</v>
+      </c>
+      <c r="L47" s="23" t="s">
+        <v>256</v>
+      </c>
+      <c r="M47" s="23" t="s">
+        <v>257</v>
+      </c>
+      <c r="N47" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O47" s="20" t="s">
+        <v>258</v>
+      </c>
+      <c r="P47" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q47" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R47" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S47" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T47" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C48" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D48" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E48" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F48" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="G48" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="H48" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="I48" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J48" s="18" t="s">
+        <v>231</v>
+      </c>
+      <c r="K48" s="19" t="s">
+        <v>261</v>
+      </c>
+      <c r="L48" s="23" t="s">
+        <v>256</v>
+      </c>
+      <c r="M48" s="23" t="s">
+        <v>262</v>
+      </c>
+      <c r="N48" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O48" s="20" t="s">
+        <v>263</v>
+      </c>
+      <c r="P48" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q48" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R48" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S48" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T48" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B49" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C49" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E49" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F49" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="G49" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="H49" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="I49" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J49" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="K49" s="19" t="s">
+        <v>264</v>
+      </c>
+      <c r="L49" s="23" t="s">
+        <v>256</v>
+      </c>
+      <c r="M49" s="23" t="s">
+        <v>262</v>
+      </c>
+      <c r="N49" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O49" s="20" t="s">
+        <v>265</v>
+      </c>
+      <c r="P49" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q49" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R49" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S49" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T49" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B50" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C50" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E50" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F50" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="G50" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="H50" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="I50" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J50" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="K50" s="19" t="s">
+        <v>266</v>
+      </c>
+      <c r="L50" s="23" t="s">
+        <v>256</v>
+      </c>
+      <c r="M50" s="23" t="s">
+        <v>262</v>
+      </c>
+      <c r="N50" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O50" s="20" t="s">
+        <v>267</v>
+      </c>
+      <c r="P50" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q50" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R50" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S50" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T50" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B51" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C51" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E51" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F51" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="G51" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="H51" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="I51" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J51" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="K51" s="19" t="s">
+        <v>269</v>
+      </c>
+      <c r="L51" s="23" t="s">
+        <v>270</v>
+      </c>
+      <c r="M51" s="23" t="s">
+        <v>271</v>
+      </c>
+      <c r="N51" s="23" t="s">
+        <v>272</v>
+      </c>
+      <c r="O51" s="20" t="s">
+        <v>273</v>
+      </c>
+      <c r="P51" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q51" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R51" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S51" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T51" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B52" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C52" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E52" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F52" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="G52" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="H52" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="I52" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J52" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="K52" s="19" t="s">
+        <v>274</v>
+      </c>
+      <c r="L52" s="23" t="s">
+        <v>270</v>
+      </c>
+      <c r="M52" s="23" t="s">
+        <v>271</v>
+      </c>
+      <c r="N52" s="23" t="s">
+        <v>272</v>
+      </c>
+      <c r="O52" s="20" t="s">
+        <v>275</v>
+      </c>
+      <c r="P52" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q52" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R52" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S52" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T52" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B53" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C53" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E53" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F53" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="G53" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="H53" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="I53" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J53" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="K53" s="19" t="s">
+        <v>276</v>
+      </c>
+      <c r="L53" s="23" t="s">
+        <v>270</v>
+      </c>
+      <c r="M53" s="23" t="s">
+        <v>271</v>
+      </c>
+      <c r="N53" s="23" t="s">
+        <v>272</v>
+      </c>
+      <c r="O53" s="20" t="s">
+        <v>277</v>
+      </c>
+      <c r="P53" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q53" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R53" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S53" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T53" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B54" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C54" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E54" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F54" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="G54" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="H54" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="I54" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J54" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="K54" s="19" t="s">
+        <v>278</v>
+      </c>
+      <c r="L54" s="23" t="s">
+        <v>270</v>
+      </c>
+      <c r="M54" s="23" t="s">
+        <v>271</v>
+      </c>
+      <c r="N54" s="23" t="s">
+        <v>272</v>
+      </c>
+      <c r="O54" s="20" t="s">
+        <v>279</v>
+      </c>
+      <c r="P54" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q54" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R54" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S54" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T54" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B55" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C55" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E55" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F55" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="G55" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="H55" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="I55" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J55" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="K55" s="19" t="s">
+        <v>280</v>
+      </c>
+      <c r="L55" s="23" t="s">
+        <v>270</v>
+      </c>
+      <c r="M55" s="23" t="s">
+        <v>271</v>
+      </c>
+      <c r="N55" s="23" t="s">
+        <v>272</v>
+      </c>
+      <c r="O55" s="20" t="s">
+        <v>281</v>
+      </c>
+      <c r="P55" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q55" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R55" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S55" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T55" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B56" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C56" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E56" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F56" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="G56" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="H56" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="I56" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J56" s="18" t="s">
+        <v>250</v>
+      </c>
+      <c r="K56" s="19" t="s">
+        <v>282</v>
+      </c>
+      <c r="L56" s="23" t="s">
+        <v>270</v>
+      </c>
+      <c r="M56" s="23" t="s">
+        <v>271</v>
+      </c>
+      <c r="N56" s="23" t="s">
+        <v>272</v>
+      </c>
+      <c r="O56" s="20" t="s">
+        <v>283</v>
+      </c>
+      <c r="P56" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q56" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R56" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S56" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T56" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B57" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C57" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E57" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F57" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="G57" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="H57" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="I57" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J57" s="18" t="s">
+        <v>239</v>
+      </c>
+      <c r="K57" s="19" t="s">
+        <v>284</v>
+      </c>
+      <c r="L57" s="23" t="s">
+        <v>270</v>
+      </c>
+      <c r="M57" s="23" t="s">
+        <v>271</v>
+      </c>
+      <c r="N57" s="23" t="s">
+        <v>272</v>
+      </c>
+      <c r="O57" s="20" t="s">
+        <v>285</v>
+      </c>
+      <c r="P57" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q57" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R57" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S57" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T57" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B58" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C58" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="E58" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F58" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="G58" s="7" t="s">
+        <v>286</v>
+      </c>
+      <c r="H58" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="I58" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J58" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="K58" s="19" t="s">
+        <v>287</v>
+      </c>
+      <c r="L58" s="23" t="s">
+        <v>270</v>
+      </c>
+      <c r="M58" s="23" t="s">
+        <v>288</v>
+      </c>
+      <c r="N58" s="23" t="s">
+        <v>289</v>
+      </c>
+      <c r="O58" s="20" t="s">
+        <v>290</v>
+      </c>
+      <c r="P58" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q58" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R58" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S58" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T58" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B59" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C59" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E59" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F59" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="G59" s="7" t="s">
+        <v>292</v>
+      </c>
+      <c r="H59" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="I59" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J59" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="K59" s="19" t="s">
+        <v>293</v>
+      </c>
+      <c r="L59" s="23" t="s">
+        <v>256</v>
+      </c>
+      <c r="M59" s="23" t="s">
+        <v>294</v>
+      </c>
+      <c r="N59" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O59" s="20" t="s">
+        <v>295</v>
+      </c>
+      <c r="P59" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q59" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R59" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S59" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T59" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B60" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C60" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="E60" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F60" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="G60" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="H60" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="I60" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J60" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="K60" s="19" t="s">
+        <v>299</v>
+      </c>
+      <c r="L60" s="23" t="s">
+        <v>300</v>
+      </c>
+      <c r="M60" s="23" t="s">
+        <v>301</v>
+      </c>
+      <c r="N60" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O60" s="20" t="s">
+        <v>302</v>
+      </c>
+      <c r="P60" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q60" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R60" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S60" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T60" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B61" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C61" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D61" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="E61" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="F61" s="8" t="s">
+        <v>304</v>
+      </c>
+      <c r="G61" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="H61" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="I61" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="J61" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="K61" s="19" t="s">
+        <v>306</v>
+      </c>
+      <c r="L61" s="23" t="s">
+        <v>307</v>
+      </c>
+      <c r="M61" s="23" t="s">
+        <v>308</v>
+      </c>
+      <c r="N61" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O61" s="20" t="s">
+        <v>309</v>
+      </c>
+      <c r="P61" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q61" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R61" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S61" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T61" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B62" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C62" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D62" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E62" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F62" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="G62" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="H62" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="I62" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J62" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="K62" s="19" t="s">
+        <v>312</v>
+      </c>
+      <c r="L62" s="23" t="s">
+        <v>313</v>
+      </c>
+      <c r="M62" s="23" t="s">
+        <v>314</v>
+      </c>
+      <c r="N62" s="23" t="s">
+        <v>315</v>
+      </c>
+      <c r="O62" s="20" t="s">
+        <v>316</v>
+      </c>
+      <c r="P62" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q62" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R62" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S62" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T62" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B63" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C63" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D63" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E63" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F63" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="G63" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="H63" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="I63" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J63" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="K63" s="19" t="s">
+        <v>318</v>
+      </c>
+      <c r="L63" s="23" t="s">
+        <v>319</v>
+      </c>
+      <c r="M63" s="23" t="s">
+        <v>320</v>
+      </c>
+      <c r="N63" s="23" t="s">
+        <v>321</v>
+      </c>
+      <c r="O63" s="20" t="s">
+        <v>322</v>
+      </c>
+      <c r="P63" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q63" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R63" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S63" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T63" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B64" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C64" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D64" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="E64" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F64" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="G64" s="7" t="s">
+        <v>323</v>
+      </c>
+      <c r="H64" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="I64" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J64" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="K64" s="19" t="s">
+        <v>324</v>
+      </c>
+      <c r="L64" s="23" t="s">
+        <v>325</v>
+      </c>
+      <c r="M64" s="23" t="s">
+        <v>326</v>
+      </c>
+      <c r="N64" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O64" s="20" t="s">
+        <v>327</v>
+      </c>
+      <c r="P64" s="13" t="s">
+        <v>328</v>
+      </c>
+      <c r="Q64" s="19" t="s">
+        <v>329</v>
+      </c>
+      <c r="R64" s="17" t="s">
+        <v>330</v>
+      </c>
+      <c r="S64" s="17" t="s">
+        <v>331</v>
+      </c>
+      <c r="T64" s="16" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B65" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C65" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D65" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E65" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="F65" s="8" t="s">
+        <v>333</v>
+      </c>
+      <c r="G65" s="7" t="s">
+        <v>334</v>
+      </c>
+      <c r="H65" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="I65" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J65" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="K65" s="19" t="s">
+        <v>335</v>
+      </c>
+      <c r="L65" s="23" t="s">
+        <v>336</v>
+      </c>
+      <c r="M65" s="23" t="s">
+        <v>337</v>
+      </c>
+      <c r="N65" s="23" t="s">
+        <v>338</v>
+      </c>
+      <c r="O65" s="20" t="s">
+        <v>339</v>
+      </c>
+      <c r="P65" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q65" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R65" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S65" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T65" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B66" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C66" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D66" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E66" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="F66" s="8" t="s">
+        <v>333</v>
+      </c>
+      <c r="G66" s="7" t="s">
+        <v>334</v>
+      </c>
+      <c r="H66" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="I66" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J66" s="18" t="s">
+        <v>231</v>
+      </c>
+      <c r="K66" s="19" t="s">
+        <v>340</v>
+      </c>
+      <c r="L66" s="23" t="s">
+        <v>336</v>
+      </c>
+      <c r="M66" s="23" t="s">
+        <v>337</v>
+      </c>
+      <c r="N66" s="23" t="s">
+        <v>338</v>
+      </c>
+      <c r="O66" s="20" t="s">
+        <v>341</v>
+      </c>
+      <c r="P66" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q66" s="19" t="s">
+        <v>342</v>
+      </c>
+      <c r="R66" s="17" t="s">
+        <v>174</v>
+      </c>
+      <c r="S66" s="17" t="s">
+        <v>175</v>
+      </c>
+      <c r="T66" s="16" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B67" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C67" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D67" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E67" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="F67" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="G67" s="7" t="s">
+        <v>344</v>
+      </c>
+      <c r="H67" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="I67" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J67" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="K67" s="19" t="s">
+        <v>345</v>
+      </c>
+      <c r="L67" s="23" t="s">
+        <v>346</v>
+      </c>
+      <c r="M67" s="23" t="s">
+        <v>347</v>
+      </c>
+      <c r="N67" s="23" t="s">
+        <v>348</v>
+      </c>
+      <c r="O67" s="20" t="s">
+        <v>349</v>
+      </c>
+      <c r="P67" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q67" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R67" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S67" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T67" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B68" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C68" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D68" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E68" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F68" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="G68" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="H68" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="I68" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J68" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="K68" s="19" t="s">
+        <v>351</v>
+      </c>
+      <c r="L68" s="23" t="s">
+        <v>256</v>
+      </c>
+      <c r="M68" s="23" t="s">
+        <v>352</v>
+      </c>
+      <c r="N68" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O68" s="20" t="s">
+        <v>353</v>
+      </c>
+      <c r="P68" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q68" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R68" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S68" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T68" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B69" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C69" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D69" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E69" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F69" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="G69" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="H69" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="I69" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J69" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="K69" s="19" t="s">
+        <v>354</v>
+      </c>
+      <c r="L69" s="23" t="s">
+        <v>256</v>
+      </c>
+      <c r="M69" s="23" t="s">
+        <v>352</v>
+      </c>
+      <c r="N69" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O69" s="20" t="s">
+        <v>355</v>
+      </c>
+      <c r="P69" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q69" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R69" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S69" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T69" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="B70" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C70" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="D70" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E70" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="F70" s="10" t="s">
+        <v>291</v>
+      </c>
+      <c r="G70" s="9" t="s">
+        <v>350</v>
+      </c>
+      <c r="H70" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="I70" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="J70" s="18" t="s">
+        <v>231</v>
+      </c>
+      <c r="K70" s="19" t="s">
+        <v>356</v>
+      </c>
+      <c r="L70" s="23" t="s">
+        <v>256</v>
+      </c>
+      <c r="M70" s="23" t="s">
+        <v>352</v>
+      </c>
+      <c r="N70" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O70" s="20" t="s">
+        <v>357</v>
+      </c>
+      <c r="P70" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q70" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R70" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S70" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T70" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B71" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C71" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D71" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E71" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F71" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="G71" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="H71" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="I71" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J71" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="K71" s="19" t="s">
+        <v>360</v>
+      </c>
+      <c r="L71" s="23" t="s">
+        <v>361</v>
+      </c>
+      <c r="M71" s="23" t="s">
+        <v>362</v>
+      </c>
+      <c r="N71" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O71" s="20" t="s">
+        <v>363</v>
+      </c>
+      <c r="P71" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q71" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R71" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S71" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T71" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B72" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C72" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D72" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E72" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F72" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="G72" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="H72" s="7" t="s">
+        <v>364</v>
+      </c>
+      <c r="I72" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J72" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="K72" s="19" t="s">
+        <v>365</v>
+      </c>
+      <c r="L72" s="23" t="s">
+        <v>361</v>
+      </c>
+      <c r="M72" s="23" t="s">
+        <v>362</v>
+      </c>
+      <c r="N72" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O72" s="20" t="s">
+        <v>366</v>
+      </c>
+      <c r="P72" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q72" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R72" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S72" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T72" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B73" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C73" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D73" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E73" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F73" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="G73" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="H73" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="I73" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J73" s="18" t="s">
+        <v>250</v>
+      </c>
+      <c r="K73" s="19" t="s">
+        <v>367</v>
+      </c>
+      <c r="L73" s="23" t="s">
+        <v>361</v>
+      </c>
+      <c r="M73" s="23" t="s">
+        <v>362</v>
+      </c>
+      <c r="N73" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O73" s="20" t="s">
+        <v>368</v>
+      </c>
+      <c r="P73" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q73" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R73" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S73" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T73" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B74" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C74" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D74" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E74" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F74" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="G74" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="H74" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="I74" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J74" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="K74" s="19" t="s">
+        <v>369</v>
+      </c>
+      <c r="L74" s="23" t="s">
+        <v>361</v>
+      </c>
+      <c r="M74" s="23" t="s">
+        <v>362</v>
+      </c>
+      <c r="N74" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O74" s="20" t="s">
+        <v>370</v>
+      </c>
+      <c r="P74" s="13" t="s">
+        <v>328</v>
+      </c>
+      <c r="Q74" s="19" t="s">
+        <v>371</v>
+      </c>
+      <c r="R74" s="17" t="s">
+        <v>372</v>
+      </c>
+      <c r="S74" s="17" t="s">
+        <v>331</v>
+      </c>
+      <c r="T74" s="16" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B75" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C75" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D75" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E75" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F75" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="G75" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="H75" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="I75" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J75" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="K75" s="19" t="s">
+        <v>374</v>
+      </c>
+      <c r="L75" s="23" t="s">
+        <v>361</v>
+      </c>
+      <c r="M75" s="23" t="s">
+        <v>362</v>
+      </c>
+      <c r="N75" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O75" s="20" t="s">
+        <v>375</v>
+      </c>
+      <c r="P75" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q75" s="19" t="s">
+        <v>376</v>
+      </c>
+      <c r="R75" s="17" t="s">
+        <v>222</v>
+      </c>
+      <c r="S75" s="17" t="s">
+        <v>175</v>
+      </c>
+      <c r="T75" s="16" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="B76" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C76" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="D76" s="10" t="s">
+        <v>378</v>
+      </c>
+      <c r="E76" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F76" s="10" t="s">
+        <v>379</v>
+      </c>
+      <c r="G76" s="9" t="s">
+        <v>380</v>
+      </c>
+      <c r="H76" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="I76" s="9" t="s">
+        <v>381</v>
+      </c>
+      <c r="J76" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="K76" s="19" t="s">
+        <v>382</v>
+      </c>
+      <c r="L76" s="23" t="s">
+        <v>383</v>
+      </c>
+      <c r="M76" s="23" t="s">
+        <v>384</v>
+      </c>
+      <c r="N76" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O76" s="20" t="s">
+        <v>385</v>
+      </c>
+      <c r="P76" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q76" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R76" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S76" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T76" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="B77" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C77" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="D77" s="10" t="s">
+        <v>378</v>
+      </c>
+      <c r="E77" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F77" s="10" t="s">
+        <v>379</v>
+      </c>
+      <c r="G77" s="9" t="s">
+        <v>380</v>
+      </c>
+      <c r="H77" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="I77" s="9" t="s">
+        <v>381</v>
+      </c>
+      <c r="J77" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="K77" s="19" t="s">
+        <v>386</v>
+      </c>
+      <c r="L77" s="23" t="s">
+        <v>383</v>
+      </c>
+      <c r="M77" s="23" t="s">
+        <v>384</v>
+      </c>
+      <c r="N77" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O77" s="20" t="s">
+        <v>387</v>
+      </c>
+      <c r="P77" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q77" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R77" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S77" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T77" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="B78" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C78" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="D78" s="10" t="s">
+        <v>378</v>
+      </c>
+      <c r="E78" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F78" s="10" t="s">
+        <v>379</v>
+      </c>
+      <c r="G78" s="9" t="s">
+        <v>380</v>
+      </c>
+      <c r="H78" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="I78" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="J78" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="K78" s="19" t="s">
+        <v>388</v>
+      </c>
+      <c r="L78" s="23" t="s">
+        <v>383</v>
+      </c>
+      <c r="M78" s="23" t="s">
+        <v>384</v>
+      </c>
+      <c r="N78" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O78" s="20" t="s">
+        <v>389</v>
+      </c>
+      <c r="P78" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q78" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R78" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S78" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T78" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="B79" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C79" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="D79" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="E79" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="F79" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G79" s="9" t="s">
+        <v>390</v>
+      </c>
+      <c r="H79" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="I79" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="J79" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="K79" s="19" t="s">
+        <v>391</v>
+      </c>
+      <c r="L79" s="23" t="s">
+        <v>392</v>
+      </c>
+      <c r="M79" s="23" t="s">
+        <v>393</v>
+      </c>
+      <c r="N79" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O79" s="20" t="s">
+        <v>394</v>
+      </c>
+      <c r="P79" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q79" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R79" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S79" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T79" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="B80" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C80" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="D80" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="E80" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="F80" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G80" s="9" t="s">
+        <v>390</v>
+      </c>
+      <c r="H80" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="I80" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="J80" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="K80" s="19" t="s">
+        <v>395</v>
+      </c>
+      <c r="L80" s="23" t="s">
+        <v>392</v>
+      </c>
+      <c r="M80" s="23" t="s">
+        <v>393</v>
+      </c>
+      <c r="N80" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O80" s="20" t="s">
+        <v>396</v>
+      </c>
+      <c r="P80" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q80" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R80" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S80" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T80" s="16" t="s">
         <v>27</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="$A$1:$T$39"/>
+  <autoFilter ref="$A$1:$T$80"/>
   <pageSetup orientation="landscape" paperSize="9"/>
   <headerFooter>
     <oddHeader>&amp;R&amp;P</oddHeader>
